--- a/VerveStacks_JPN/SysSettings.xlsx
+++ b/VerveStacks_JPN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18DF10C-5C51-4C0F-BBA2-F472BCBE4C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D459409-9A8E-4259-A7C7-42C41A774AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_JPN/SysSettings.xlsx
+++ b/VerveStacks_JPN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D459409-9A8E-4259-A7C7-42C41A774AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B421198-C9D8-44C1-AB4A-D4259AE64992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_JPN/SysSettings.xlsx
+++ b/VerveStacks_JPN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B421198-C9D8-44C1-AB4A-D4259AE64992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E862F9A6-E5BA-4589-A7E7-8656C3E62160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_JPN/SysSettings.xlsx
+++ b/VerveStacks_JPN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E862F9A6-E5BA-4589-A7E7-8656C3E62160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C7B0A6-67D3-4C49-8975-8C48160FAEB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_JPN/SysSettings.xlsx
+++ b/VerveStacks_JPN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C7B0A6-67D3-4C49-8975-8C48160FAEB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C8E069-AAF4-4DA0-B0A6-6019932F19C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_JPN/SysSettings.xlsx
+++ b/VerveStacks_JPN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C8E069-AAF4-4DA0-B0A6-6019932F19C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E0C0C8-4A1D-4CC2-8530-767635902C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_JPN/SysSettings.xlsx
+++ b/VerveStacks_JPN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E0C0C8-4A1D-4CC2-8530-767635902C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD05688-73D6-483A-872F-0B16AE11EAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_JPN/SysSettings.xlsx
+++ b/VerveStacks_JPN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD05688-73D6-483A-872F-0B16AE11EAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6BE4F8-1D75-48EF-BB25-73AF23904313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_JPN/SysSettings.xlsx
+++ b/VerveStacks_JPN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6BE4F8-1D75-48EF-BB25-73AF23904313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6558B80-B59B-4E59-911F-6E94821FFE19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_JPN/SysSettings.xlsx
+++ b/VerveStacks_JPN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6558B80-B59B-4E59-911F-6E94821FFE19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2585AB4-2FA8-4C1A-B10B-2BA3D859B86D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_JPN/SysSettings.xlsx
+++ b/VerveStacks_JPN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2585AB4-2FA8-4C1A-B10B-2BA3D859B86D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E677259D-F9CF-4C44-9012-0F23D0FBB736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_JPN/SysSettings.xlsx
+++ b/VerveStacks_JPN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E677259D-F9CF-4C44-9012-0F23D0FBB736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E171CAAD-095A-451A-A57E-A437606FA987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="427">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -682,25 +682,643 @@
     <t>set</t>
   </si>
   <si>
-    <t>elc_spv-JPN</t>
-  </si>
-  <si>
-    <t>solar electricity generation</t>
+    <t>elc_spv_001</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 1</t>
   </si>
   <si>
     <t>TWh</t>
   </si>
   <si>
-    <t>elc_wof-JPN</t>
-  </si>
-  <si>
-    <t>offshore wind electricity generation</t>
-  </si>
-  <si>
-    <t>elc_won-JPN</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation</t>
+    <t>elc_spv_002</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 2</t>
+  </si>
+  <si>
+    <t>elc_spv_003</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 3</t>
+  </si>
+  <si>
+    <t>elc_spv_004</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 4</t>
+  </si>
+  <si>
+    <t>elc_spv_005</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 5</t>
+  </si>
+  <si>
+    <t>elc_spv_006</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 6</t>
+  </si>
+  <si>
+    <t>elc_spv_007</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 7</t>
+  </si>
+  <si>
+    <t>elc_spv_008</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 8</t>
+  </si>
+  <si>
+    <t>elc_spv_009</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 9</t>
+  </si>
+  <si>
+    <t>elc_spv_010</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 10</t>
+  </si>
+  <si>
+    <t>elc_spv_011</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 11</t>
+  </si>
+  <si>
+    <t>elc_spv_012</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 12</t>
+  </si>
+  <si>
+    <t>elc_spv_013</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 13</t>
+  </si>
+  <si>
+    <t>elc_spv_014</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 14</t>
+  </si>
+  <si>
+    <t>elc_spv_015</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 15</t>
+  </si>
+  <si>
+    <t>elc_spv_016</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 16</t>
+  </si>
+  <si>
+    <t>elc_spv_017</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 17</t>
+  </si>
+  <si>
+    <t>elc_spv_018</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 18</t>
+  </si>
+  <si>
+    <t>elc_spv_019</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 19</t>
+  </si>
+  <si>
+    <t>elc_spv_020</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 20</t>
+  </si>
+  <si>
+    <t>elc_spv_021</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 21</t>
+  </si>
+  <si>
+    <t>elc_spv_022</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 22</t>
+  </si>
+  <si>
+    <t>elc_spv_023</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 23</t>
+  </si>
+  <si>
+    <t>elc_spv_024</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 24</t>
+  </si>
+  <si>
+    <t>elc_spv_025</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 25</t>
+  </si>
+  <si>
+    <t>elc_spv_026</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 26</t>
+  </si>
+  <si>
+    <t>elc_spv_027</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 27</t>
+  </si>
+  <si>
+    <t>elc_spv_028</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 28</t>
+  </si>
+  <si>
+    <t>elc_spv_029</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 29</t>
+  </si>
+  <si>
+    <t>elc_spv_030</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 30</t>
+  </si>
+  <si>
+    <t>elc_spv_031</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 31</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 1</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 2</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 3</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 4</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 5</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 6</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 7</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 8</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 9</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 10</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 11</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 12</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 13</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 14</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 15</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 16</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 17</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 18</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 19</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 20</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 21</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 22</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 23</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 24</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 25</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 26</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 27</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 28</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 29</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 30</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 31</t>
+  </si>
+  <si>
+    <t>elc_wof_032</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 32</t>
+  </si>
+  <si>
+    <t>elc_wof_033</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 33</t>
+  </si>
+  <si>
+    <t>elc_wof_034</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 34</t>
+  </si>
+  <si>
+    <t>elc_wof_035</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 35</t>
+  </si>
+  <si>
+    <t>elc_wof_036</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 36</t>
+  </si>
+  <si>
+    <t>elc_wof_037</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 37</t>
+  </si>
+  <si>
+    <t>elc_wof_038</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 38</t>
+  </si>
+  <si>
+    <t>elc_wof_039</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 39</t>
+  </si>
+  <si>
+    <t>elc_wof_040</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 40</t>
+  </si>
+  <si>
+    <t>elc_wof_041</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 41</t>
+  </si>
+  <si>
+    <t>elc_wof_042</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 42</t>
+  </si>
+  <si>
+    <t>elc_wof_043</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 43</t>
+  </si>
+  <si>
+    <t>elc_wof_044</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 44</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 1</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 2</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 3</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 4</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 5</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 6</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 7</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 8</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 9</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 10</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 11</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 12</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 13</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 14</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 15</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 16</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 17</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 18</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 19</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 20</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 21</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 22</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 23</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 24</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 25</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 26</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 27</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 28</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 29</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 30</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 31</t>
   </si>
 </sst>
 </file>
@@ -3116,7 +3734,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:R24"/>
+  <dimension ref="B3:R110"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
@@ -3289,6 +3907,24 @@
       <c r="E8" t="s">
         <v>18</v>
       </c>
+      <c r="M8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" t="s">
+        <v>221</v>
+      </c>
+      <c r="O8" t="s">
+        <v>222</v>
+      </c>
+      <c r="P8" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>35</v>
+      </c>
+      <c r="R8" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="9" spans="2:18">
       <c r="B9" t="s">
@@ -3300,6 +3936,24 @@
       <c r="E9" t="s">
         <v>18</v>
       </c>
+      <c r="M9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" t="s">
+        <v>223</v>
+      </c>
+      <c r="O9" t="s">
+        <v>224</v>
+      </c>
+      <c r="P9" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>35</v>
+      </c>
+      <c r="R9" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="10" spans="2:18">
       <c r="B10" t="s">
@@ -3311,6 +3965,24 @@
       <c r="E10" t="s">
         <v>18</v>
       </c>
+      <c r="M10" t="s">
+        <v>17</v>
+      </c>
+      <c r="N10" t="s">
+        <v>225</v>
+      </c>
+      <c r="O10" t="s">
+        <v>226</v>
+      </c>
+      <c r="P10" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>35</v>
+      </c>
+      <c r="R10" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="11" spans="2:18">
       <c r="B11" t="s">
@@ -3322,6 +3994,24 @@
       <c r="E11" t="s">
         <v>18</v>
       </c>
+      <c r="M11" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" t="s">
+        <v>227</v>
+      </c>
+      <c r="O11" t="s">
+        <v>228</v>
+      </c>
+      <c r="P11" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R11" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="12" spans="2:18">
       <c r="B12" t="s">
@@ -3333,6 +4023,24 @@
       <c r="E12" t="s">
         <v>18</v>
       </c>
+      <c r="M12" t="s">
+        <v>17</v>
+      </c>
+      <c r="N12" t="s">
+        <v>229</v>
+      </c>
+      <c r="O12" t="s">
+        <v>230</v>
+      </c>
+      <c r="P12" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>35</v>
+      </c>
+      <c r="R12" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="13" spans="2:18">
       <c r="B13" t="s">
@@ -3344,6 +4052,24 @@
       <c r="E13" t="s">
         <v>18</v>
       </c>
+      <c r="M13" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" t="s">
+        <v>231</v>
+      </c>
+      <c r="O13" t="s">
+        <v>232</v>
+      </c>
+      <c r="P13" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>35</v>
+      </c>
+      <c r="R13" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="14" spans="2:18">
       <c r="B14" t="s">
@@ -3358,6 +4084,24 @@
       <c r="E14" t="s">
         <v>18</v>
       </c>
+      <c r="M14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" t="s">
+        <v>233</v>
+      </c>
+      <c r="O14" t="s">
+        <v>234</v>
+      </c>
+      <c r="P14" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>35</v>
+      </c>
+      <c r="R14" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="15" spans="2:18">
       <c r="B15" t="s">
@@ -3372,6 +4116,24 @@
       <c r="E15" t="s">
         <v>18</v>
       </c>
+      <c r="M15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" t="s">
+        <v>235</v>
+      </c>
+      <c r="O15" t="s">
+        <v>236</v>
+      </c>
+      <c r="P15" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>35</v>
+      </c>
+      <c r="R15" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="16" spans="2:18">
       <c r="B16" t="s">
@@ -3395,8 +4157,26 @@
       <c r="I16" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="17" spans="2:7">
+      <c r="M16" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" t="s">
+        <v>237</v>
+      </c>
+      <c r="O16" t="s">
+        <v>238</v>
+      </c>
+      <c r="P16" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>35</v>
+      </c>
+      <c r="R16" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18">
       <c r="B17" t="s">
         <v>34</v>
       </c>
@@ -3409,8 +4189,26 @@
       <c r="E17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="2:7">
+      <c r="M17" t="s">
+        <v>17</v>
+      </c>
+      <c r="N17" t="s">
+        <v>239</v>
+      </c>
+      <c r="O17" t="s">
+        <v>240</v>
+      </c>
+      <c r="P17" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>35</v>
+      </c>
+      <c r="R17" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18">
       <c r="B18" t="s">
         <v>34</v>
       </c>
@@ -3423,8 +4221,26 @@
       <c r="E18" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="2:7">
+      <c r="M18" t="s">
+        <v>17</v>
+      </c>
+      <c r="N18" t="s">
+        <v>241</v>
+      </c>
+      <c r="O18" t="s">
+        <v>242</v>
+      </c>
+      <c r="P18" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R18" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18">
       <c r="B19" t="s">
         <v>34</v>
       </c>
@@ -3437,8 +4253,26 @@
       <c r="E19" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="2:7">
+      <c r="M19" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19" t="s">
+        <v>243</v>
+      </c>
+      <c r="O19" t="s">
+        <v>244</v>
+      </c>
+      <c r="P19" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>35</v>
+      </c>
+      <c r="R19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18">
       <c r="B20" t="s">
         <v>34</v>
       </c>
@@ -3451,8 +4285,26 @@
       <c r="E20" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="2:7">
+      <c r="M20" t="s">
+        <v>17</v>
+      </c>
+      <c r="N20" t="s">
+        <v>245</v>
+      </c>
+      <c r="O20" t="s">
+        <v>246</v>
+      </c>
+      <c r="P20" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>35</v>
+      </c>
+      <c r="R20" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18">
       <c r="B21" t="s">
         <v>17</v>
       </c>
@@ -3471,8 +4323,26 @@
       <c r="G21" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="2:7">
+      <c r="M21" t="s">
+        <v>17</v>
+      </c>
+      <c r="N21" t="s">
+        <v>247</v>
+      </c>
+      <c r="O21" t="s">
+        <v>248</v>
+      </c>
+      <c r="P21" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>35</v>
+      </c>
+      <c r="R21" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18">
       <c r="B22" t="s">
         <v>193</v>
       </c>
@@ -3485,8 +4355,26 @@
       <c r="E22" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="23" spans="2:7">
+      <c r="M22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N22" t="s">
+        <v>249</v>
+      </c>
+      <c r="O22" t="s">
+        <v>250</v>
+      </c>
+      <c r="P22" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>35</v>
+      </c>
+      <c r="R22" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18">
       <c r="B23" t="s">
         <v>193</v>
       </c>
@@ -3496,8 +4384,26 @@
       <c r="E23" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="24" spans="2:7">
+      <c r="M23" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" t="s">
+        <v>251</v>
+      </c>
+      <c r="O23" t="s">
+        <v>252</v>
+      </c>
+      <c r="P23" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>35</v>
+      </c>
+      <c r="R23" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18">
       <c r="B24" t="s">
         <v>193</v>
       </c>
@@ -3506,6 +4412,1744 @@
       </c>
       <c r="E24" t="s">
         <v>196</v>
+      </c>
+      <c r="M24" t="s">
+        <v>17</v>
+      </c>
+      <c r="N24" t="s">
+        <v>253</v>
+      </c>
+      <c r="O24" t="s">
+        <v>254</v>
+      </c>
+      <c r="P24" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>35</v>
+      </c>
+      <c r="R24" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18">
+      <c r="M25" t="s">
+        <v>17</v>
+      </c>
+      <c r="N25" t="s">
+        <v>255</v>
+      </c>
+      <c r="O25" t="s">
+        <v>256</v>
+      </c>
+      <c r="P25" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>35</v>
+      </c>
+      <c r="R25" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18">
+      <c r="M26" t="s">
+        <v>17</v>
+      </c>
+      <c r="N26" t="s">
+        <v>257</v>
+      </c>
+      <c r="O26" t="s">
+        <v>258</v>
+      </c>
+      <c r="P26" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>35</v>
+      </c>
+      <c r="R26" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18">
+      <c r="M27" t="s">
+        <v>17</v>
+      </c>
+      <c r="N27" t="s">
+        <v>259</v>
+      </c>
+      <c r="O27" t="s">
+        <v>260</v>
+      </c>
+      <c r="P27" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>35</v>
+      </c>
+      <c r="R27" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18">
+      <c r="M28" t="s">
+        <v>17</v>
+      </c>
+      <c r="N28" t="s">
+        <v>261</v>
+      </c>
+      <c r="O28" t="s">
+        <v>262</v>
+      </c>
+      <c r="P28" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R28" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18">
+      <c r="M29" t="s">
+        <v>17</v>
+      </c>
+      <c r="N29" t="s">
+        <v>263</v>
+      </c>
+      <c r="O29" t="s">
+        <v>264</v>
+      </c>
+      <c r="P29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>35</v>
+      </c>
+      <c r="R29" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18">
+      <c r="M30" t="s">
+        <v>17</v>
+      </c>
+      <c r="N30" t="s">
+        <v>265</v>
+      </c>
+      <c r="O30" t="s">
+        <v>266</v>
+      </c>
+      <c r="P30" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>35</v>
+      </c>
+      <c r="R30" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18">
+      <c r="M31" t="s">
+        <v>17</v>
+      </c>
+      <c r="N31" t="s">
+        <v>267</v>
+      </c>
+      <c r="O31" t="s">
+        <v>268</v>
+      </c>
+      <c r="P31" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>35</v>
+      </c>
+      <c r="R31" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18">
+      <c r="M32" t="s">
+        <v>17</v>
+      </c>
+      <c r="N32" t="s">
+        <v>269</v>
+      </c>
+      <c r="O32" t="s">
+        <v>270</v>
+      </c>
+      <c r="P32" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>35</v>
+      </c>
+      <c r="R32" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="33" spans="13:18">
+      <c r="M33" t="s">
+        <v>17</v>
+      </c>
+      <c r="N33" t="s">
+        <v>271</v>
+      </c>
+      <c r="O33" t="s">
+        <v>272</v>
+      </c>
+      <c r="P33" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>35</v>
+      </c>
+      <c r="R33" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="34" spans="13:18">
+      <c r="M34" t="s">
+        <v>17</v>
+      </c>
+      <c r="N34" t="s">
+        <v>273</v>
+      </c>
+      <c r="O34" t="s">
+        <v>274</v>
+      </c>
+      <c r="P34" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>35</v>
+      </c>
+      <c r="R34" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="35" spans="13:18">
+      <c r="M35" t="s">
+        <v>17</v>
+      </c>
+      <c r="N35" t="s">
+        <v>275</v>
+      </c>
+      <c r="O35" t="s">
+        <v>276</v>
+      </c>
+      <c r="P35" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>35</v>
+      </c>
+      <c r="R35" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="36" spans="13:18">
+      <c r="M36" t="s">
+        <v>17</v>
+      </c>
+      <c r="N36" t="s">
+        <v>277</v>
+      </c>
+      <c r="O36" t="s">
+        <v>278</v>
+      </c>
+      <c r="P36" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>35</v>
+      </c>
+      <c r="R36" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="37" spans="13:18">
+      <c r="M37" t="s">
+        <v>17</v>
+      </c>
+      <c r="N37" t="s">
+        <v>279</v>
+      </c>
+      <c r="O37" t="s">
+        <v>280</v>
+      </c>
+      <c r="P37" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>35</v>
+      </c>
+      <c r="R37" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="38" spans="13:18">
+      <c r="M38" t="s">
+        <v>17</v>
+      </c>
+      <c r="N38" t="s">
+        <v>281</v>
+      </c>
+      <c r="O38" t="s">
+        <v>282</v>
+      </c>
+      <c r="P38" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>35</v>
+      </c>
+      <c r="R38" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="39" spans="13:18">
+      <c r="M39" t="s">
+        <v>17</v>
+      </c>
+      <c r="N39" t="s">
+        <v>283</v>
+      </c>
+      <c r="O39" t="s">
+        <v>284</v>
+      </c>
+      <c r="P39" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>35</v>
+      </c>
+      <c r="R39" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="40" spans="13:18">
+      <c r="M40" t="s">
+        <v>17</v>
+      </c>
+      <c r="N40" t="s">
+        <v>285</v>
+      </c>
+      <c r="O40" t="s">
+        <v>286</v>
+      </c>
+      <c r="P40" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>35</v>
+      </c>
+      <c r="R40" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="41" spans="13:18">
+      <c r="M41" t="s">
+        <v>17</v>
+      </c>
+      <c r="N41" t="s">
+        <v>287</v>
+      </c>
+      <c r="O41" t="s">
+        <v>288</v>
+      </c>
+      <c r="P41" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>35</v>
+      </c>
+      <c r="R41" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="42" spans="13:18">
+      <c r="M42" t="s">
+        <v>17</v>
+      </c>
+      <c r="N42" t="s">
+        <v>289</v>
+      </c>
+      <c r="O42" t="s">
+        <v>290</v>
+      </c>
+      <c r="P42" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>35</v>
+      </c>
+      <c r="R42" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="43" spans="13:18">
+      <c r="M43" t="s">
+        <v>17</v>
+      </c>
+      <c r="N43" t="s">
+        <v>291</v>
+      </c>
+      <c r="O43" t="s">
+        <v>292</v>
+      </c>
+      <c r="P43" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>35</v>
+      </c>
+      <c r="R43" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="44" spans="13:18">
+      <c r="M44" t="s">
+        <v>17</v>
+      </c>
+      <c r="N44" t="s">
+        <v>293</v>
+      </c>
+      <c r="O44" t="s">
+        <v>294</v>
+      </c>
+      <c r="P44" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>35</v>
+      </c>
+      <c r="R44" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="45" spans="13:18">
+      <c r="M45" t="s">
+        <v>17</v>
+      </c>
+      <c r="N45" t="s">
+        <v>295</v>
+      </c>
+      <c r="O45" t="s">
+        <v>296</v>
+      </c>
+      <c r="P45" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>35</v>
+      </c>
+      <c r="R45" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="46" spans="13:18">
+      <c r="M46" t="s">
+        <v>17</v>
+      </c>
+      <c r="N46" t="s">
+        <v>297</v>
+      </c>
+      <c r="O46" t="s">
+        <v>298</v>
+      </c>
+      <c r="P46" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>35</v>
+      </c>
+      <c r="R46" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="47" spans="13:18">
+      <c r="M47" t="s">
+        <v>17</v>
+      </c>
+      <c r="N47" t="s">
+        <v>299</v>
+      </c>
+      <c r="O47" t="s">
+        <v>300</v>
+      </c>
+      <c r="P47" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>35</v>
+      </c>
+      <c r="R47" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="48" spans="13:18">
+      <c r="M48" t="s">
+        <v>17</v>
+      </c>
+      <c r="N48" t="s">
+        <v>301</v>
+      </c>
+      <c r="O48" t="s">
+        <v>302</v>
+      </c>
+      <c r="P48" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>35</v>
+      </c>
+      <c r="R48" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="49" spans="13:18">
+      <c r="M49" t="s">
+        <v>17</v>
+      </c>
+      <c r="N49" t="s">
+        <v>303</v>
+      </c>
+      <c r="O49" t="s">
+        <v>304</v>
+      </c>
+      <c r="P49" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>35</v>
+      </c>
+      <c r="R49" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="50" spans="13:18">
+      <c r="M50" t="s">
+        <v>17</v>
+      </c>
+      <c r="N50" t="s">
+        <v>305</v>
+      </c>
+      <c r="O50" t="s">
+        <v>306</v>
+      </c>
+      <c r="P50" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>35</v>
+      </c>
+      <c r="R50" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="51" spans="13:18">
+      <c r="M51" t="s">
+        <v>17</v>
+      </c>
+      <c r="N51" t="s">
+        <v>307</v>
+      </c>
+      <c r="O51" t="s">
+        <v>308</v>
+      </c>
+      <c r="P51" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>35</v>
+      </c>
+      <c r="R51" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="52" spans="13:18">
+      <c r="M52" t="s">
+        <v>17</v>
+      </c>
+      <c r="N52" t="s">
+        <v>309</v>
+      </c>
+      <c r="O52" t="s">
+        <v>310</v>
+      </c>
+      <c r="P52" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>35</v>
+      </c>
+      <c r="R52" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="53" spans="13:18">
+      <c r="M53" t="s">
+        <v>17</v>
+      </c>
+      <c r="N53" t="s">
+        <v>311</v>
+      </c>
+      <c r="O53" t="s">
+        <v>312</v>
+      </c>
+      <c r="P53" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>35</v>
+      </c>
+      <c r="R53" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="54" spans="13:18">
+      <c r="M54" t="s">
+        <v>17</v>
+      </c>
+      <c r="N54" t="s">
+        <v>313</v>
+      </c>
+      <c r="O54" t="s">
+        <v>314</v>
+      </c>
+      <c r="P54" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>35</v>
+      </c>
+      <c r="R54" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="55" spans="13:18">
+      <c r="M55" t="s">
+        <v>17</v>
+      </c>
+      <c r="N55" t="s">
+        <v>315</v>
+      </c>
+      <c r="O55" t="s">
+        <v>316</v>
+      </c>
+      <c r="P55" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>35</v>
+      </c>
+      <c r="R55" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="56" spans="13:18">
+      <c r="M56" t="s">
+        <v>17</v>
+      </c>
+      <c r="N56" t="s">
+        <v>317</v>
+      </c>
+      <c r="O56" t="s">
+        <v>318</v>
+      </c>
+      <c r="P56" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>35</v>
+      </c>
+      <c r="R56" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="57" spans="13:18">
+      <c r="M57" t="s">
+        <v>17</v>
+      </c>
+      <c r="N57" t="s">
+        <v>319</v>
+      </c>
+      <c r="O57" t="s">
+        <v>320</v>
+      </c>
+      <c r="P57" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>35</v>
+      </c>
+      <c r="R57" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="58" spans="13:18">
+      <c r="M58" t="s">
+        <v>17</v>
+      </c>
+      <c r="N58" t="s">
+        <v>321</v>
+      </c>
+      <c r="O58" t="s">
+        <v>322</v>
+      </c>
+      <c r="P58" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>35</v>
+      </c>
+      <c r="R58" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="59" spans="13:18">
+      <c r="M59" t="s">
+        <v>17</v>
+      </c>
+      <c r="N59" t="s">
+        <v>323</v>
+      </c>
+      <c r="O59" t="s">
+        <v>324</v>
+      </c>
+      <c r="P59" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>35</v>
+      </c>
+      <c r="R59" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="60" spans="13:18">
+      <c r="M60" t="s">
+        <v>17</v>
+      </c>
+      <c r="N60" t="s">
+        <v>325</v>
+      </c>
+      <c r="O60" t="s">
+        <v>326</v>
+      </c>
+      <c r="P60" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>35</v>
+      </c>
+      <c r="R60" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="61" spans="13:18">
+      <c r="M61" t="s">
+        <v>17</v>
+      </c>
+      <c r="N61" t="s">
+        <v>327</v>
+      </c>
+      <c r="O61" t="s">
+        <v>328</v>
+      </c>
+      <c r="P61" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>35</v>
+      </c>
+      <c r="R61" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="62" spans="13:18">
+      <c r="M62" t="s">
+        <v>17</v>
+      </c>
+      <c r="N62" t="s">
+        <v>329</v>
+      </c>
+      <c r="O62" t="s">
+        <v>330</v>
+      </c>
+      <c r="P62" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>35</v>
+      </c>
+      <c r="R62" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="63" spans="13:18">
+      <c r="M63" t="s">
+        <v>17</v>
+      </c>
+      <c r="N63" t="s">
+        <v>331</v>
+      </c>
+      <c r="O63" t="s">
+        <v>332</v>
+      </c>
+      <c r="P63" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>35</v>
+      </c>
+      <c r="R63" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="64" spans="13:18">
+      <c r="M64" t="s">
+        <v>17</v>
+      </c>
+      <c r="N64" t="s">
+        <v>333</v>
+      </c>
+      <c r="O64" t="s">
+        <v>334</v>
+      </c>
+      <c r="P64" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>35</v>
+      </c>
+      <c r="R64" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="65" spans="13:18">
+      <c r="M65" t="s">
+        <v>17</v>
+      </c>
+      <c r="N65" t="s">
+        <v>335</v>
+      </c>
+      <c r="O65" t="s">
+        <v>336</v>
+      </c>
+      <c r="P65" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>35</v>
+      </c>
+      <c r="R65" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="66" spans="13:18">
+      <c r="M66" t="s">
+        <v>17</v>
+      </c>
+      <c r="N66" t="s">
+        <v>337</v>
+      </c>
+      <c r="O66" t="s">
+        <v>338</v>
+      </c>
+      <c r="P66" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>35</v>
+      </c>
+      <c r="R66" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="67" spans="13:18">
+      <c r="M67" t="s">
+        <v>17</v>
+      </c>
+      <c r="N67" t="s">
+        <v>339</v>
+      </c>
+      <c r="O67" t="s">
+        <v>340</v>
+      </c>
+      <c r="P67" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>35</v>
+      </c>
+      <c r="R67" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="68" spans="13:18">
+      <c r="M68" t="s">
+        <v>17</v>
+      </c>
+      <c r="N68" t="s">
+        <v>341</v>
+      </c>
+      <c r="O68" t="s">
+        <v>342</v>
+      </c>
+      <c r="P68" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>35</v>
+      </c>
+      <c r="R68" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="69" spans="13:18">
+      <c r="M69" t="s">
+        <v>17</v>
+      </c>
+      <c r="N69" t="s">
+        <v>343</v>
+      </c>
+      <c r="O69" t="s">
+        <v>344</v>
+      </c>
+      <c r="P69" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>35</v>
+      </c>
+      <c r="R69" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="70" spans="13:18">
+      <c r="M70" t="s">
+        <v>17</v>
+      </c>
+      <c r="N70" t="s">
+        <v>345</v>
+      </c>
+      <c r="O70" t="s">
+        <v>346</v>
+      </c>
+      <c r="P70" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>35</v>
+      </c>
+      <c r="R70" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="71" spans="13:18">
+      <c r="M71" t="s">
+        <v>17</v>
+      </c>
+      <c r="N71" t="s">
+        <v>347</v>
+      </c>
+      <c r="O71" t="s">
+        <v>348</v>
+      </c>
+      <c r="P71" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>35</v>
+      </c>
+      <c r="R71" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="72" spans="13:18">
+      <c r="M72" t="s">
+        <v>17</v>
+      </c>
+      <c r="N72" t="s">
+        <v>349</v>
+      </c>
+      <c r="O72" t="s">
+        <v>350</v>
+      </c>
+      <c r="P72" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>35</v>
+      </c>
+      <c r="R72" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="73" spans="13:18">
+      <c r="M73" t="s">
+        <v>17</v>
+      </c>
+      <c r="N73" t="s">
+        <v>351</v>
+      </c>
+      <c r="O73" t="s">
+        <v>352</v>
+      </c>
+      <c r="P73" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>35</v>
+      </c>
+      <c r="R73" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="74" spans="13:18">
+      <c r="M74" t="s">
+        <v>17</v>
+      </c>
+      <c r="N74" t="s">
+        <v>353</v>
+      </c>
+      <c r="O74" t="s">
+        <v>354</v>
+      </c>
+      <c r="P74" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>35</v>
+      </c>
+      <c r="R74" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="75" spans="13:18">
+      <c r="M75" t="s">
+        <v>17</v>
+      </c>
+      <c r="N75" t="s">
+        <v>355</v>
+      </c>
+      <c r="O75" t="s">
+        <v>356</v>
+      </c>
+      <c r="P75" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>35</v>
+      </c>
+      <c r="R75" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="76" spans="13:18">
+      <c r="M76" t="s">
+        <v>17</v>
+      </c>
+      <c r="N76" t="s">
+        <v>357</v>
+      </c>
+      <c r="O76" t="s">
+        <v>358</v>
+      </c>
+      <c r="P76" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>35</v>
+      </c>
+      <c r="R76" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="77" spans="13:18">
+      <c r="M77" t="s">
+        <v>17</v>
+      </c>
+      <c r="N77" t="s">
+        <v>359</v>
+      </c>
+      <c r="O77" t="s">
+        <v>360</v>
+      </c>
+      <c r="P77" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>35</v>
+      </c>
+      <c r="R77" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="78" spans="13:18">
+      <c r="M78" t="s">
+        <v>17</v>
+      </c>
+      <c r="N78" t="s">
+        <v>361</v>
+      </c>
+      <c r="O78" t="s">
+        <v>362</v>
+      </c>
+      <c r="P78" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>35</v>
+      </c>
+      <c r="R78" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="79" spans="13:18">
+      <c r="M79" t="s">
+        <v>17</v>
+      </c>
+      <c r="N79" t="s">
+        <v>363</v>
+      </c>
+      <c r="O79" t="s">
+        <v>364</v>
+      </c>
+      <c r="P79" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>35</v>
+      </c>
+      <c r="R79" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="80" spans="13:18">
+      <c r="M80" t="s">
+        <v>17</v>
+      </c>
+      <c r="N80" t="s">
+        <v>365</v>
+      </c>
+      <c r="O80" t="s">
+        <v>366</v>
+      </c>
+      <c r="P80" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>35</v>
+      </c>
+      <c r="R80" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="81" spans="13:18">
+      <c r="M81" t="s">
+        <v>17</v>
+      </c>
+      <c r="N81" t="s">
+        <v>367</v>
+      </c>
+      <c r="O81" t="s">
+        <v>368</v>
+      </c>
+      <c r="P81" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>35</v>
+      </c>
+      <c r="R81" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="82" spans="13:18">
+      <c r="M82" t="s">
+        <v>17</v>
+      </c>
+      <c r="N82" t="s">
+        <v>369</v>
+      </c>
+      <c r="O82" t="s">
+        <v>370</v>
+      </c>
+      <c r="P82" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>35</v>
+      </c>
+      <c r="R82" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="83" spans="13:18">
+      <c r="M83" t="s">
+        <v>17</v>
+      </c>
+      <c r="N83" t="s">
+        <v>371</v>
+      </c>
+      <c r="O83" t="s">
+        <v>372</v>
+      </c>
+      <c r="P83" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>35</v>
+      </c>
+      <c r="R83" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="84" spans="13:18">
+      <c r="M84" t="s">
+        <v>17</v>
+      </c>
+      <c r="N84" t="s">
+        <v>373</v>
+      </c>
+      <c r="O84" t="s">
+        <v>374</v>
+      </c>
+      <c r="P84" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>35</v>
+      </c>
+      <c r="R84" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="85" spans="13:18">
+      <c r="M85" t="s">
+        <v>17</v>
+      </c>
+      <c r="N85" t="s">
+        <v>375</v>
+      </c>
+      <c r="O85" t="s">
+        <v>376</v>
+      </c>
+      <c r="P85" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>35</v>
+      </c>
+      <c r="R85" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="86" spans="13:18">
+      <c r="M86" t="s">
+        <v>17</v>
+      </c>
+      <c r="N86" t="s">
+        <v>377</v>
+      </c>
+      <c r="O86" t="s">
+        <v>378</v>
+      </c>
+      <c r="P86" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>35</v>
+      </c>
+      <c r="R86" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="87" spans="13:18">
+      <c r="M87" t="s">
+        <v>17</v>
+      </c>
+      <c r="N87" t="s">
+        <v>379</v>
+      </c>
+      <c r="O87" t="s">
+        <v>380</v>
+      </c>
+      <c r="P87" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>35</v>
+      </c>
+      <c r="R87" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="88" spans="13:18">
+      <c r="M88" t="s">
+        <v>17</v>
+      </c>
+      <c r="N88" t="s">
+        <v>381</v>
+      </c>
+      <c r="O88" t="s">
+        <v>382</v>
+      </c>
+      <c r="P88" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>35</v>
+      </c>
+      <c r="R88" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="89" spans="13:18">
+      <c r="M89" t="s">
+        <v>17</v>
+      </c>
+      <c r="N89" t="s">
+        <v>383</v>
+      </c>
+      <c r="O89" t="s">
+        <v>384</v>
+      </c>
+      <c r="P89" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>35</v>
+      </c>
+      <c r="R89" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="90" spans="13:18">
+      <c r="M90" t="s">
+        <v>17</v>
+      </c>
+      <c r="N90" t="s">
+        <v>385</v>
+      </c>
+      <c r="O90" t="s">
+        <v>386</v>
+      </c>
+      <c r="P90" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>35</v>
+      </c>
+      <c r="R90" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="91" spans="13:18">
+      <c r="M91" t="s">
+        <v>17</v>
+      </c>
+      <c r="N91" t="s">
+        <v>387</v>
+      </c>
+      <c r="O91" t="s">
+        <v>388</v>
+      </c>
+      <c r="P91" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>35</v>
+      </c>
+      <c r="R91" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="92" spans="13:18">
+      <c r="M92" t="s">
+        <v>17</v>
+      </c>
+      <c r="N92" t="s">
+        <v>389</v>
+      </c>
+      <c r="O92" t="s">
+        <v>390</v>
+      </c>
+      <c r="P92" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>35</v>
+      </c>
+      <c r="R92" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="93" spans="13:18">
+      <c r="M93" t="s">
+        <v>17</v>
+      </c>
+      <c r="N93" t="s">
+        <v>391</v>
+      </c>
+      <c r="O93" t="s">
+        <v>392</v>
+      </c>
+      <c r="P93" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>35</v>
+      </c>
+      <c r="R93" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="94" spans="13:18">
+      <c r="M94" t="s">
+        <v>17</v>
+      </c>
+      <c r="N94" t="s">
+        <v>393</v>
+      </c>
+      <c r="O94" t="s">
+        <v>394</v>
+      </c>
+      <c r="P94" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>35</v>
+      </c>
+      <c r="R94" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="95" spans="13:18">
+      <c r="M95" t="s">
+        <v>17</v>
+      </c>
+      <c r="N95" t="s">
+        <v>395</v>
+      </c>
+      <c r="O95" t="s">
+        <v>396</v>
+      </c>
+      <c r="P95" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>35</v>
+      </c>
+      <c r="R95" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="96" spans="13:18">
+      <c r="M96" t="s">
+        <v>17</v>
+      </c>
+      <c r="N96" t="s">
+        <v>397</v>
+      </c>
+      <c r="O96" t="s">
+        <v>398</v>
+      </c>
+      <c r="P96" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>35</v>
+      </c>
+      <c r="R96" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="97" spans="13:18">
+      <c r="M97" t="s">
+        <v>17</v>
+      </c>
+      <c r="N97" t="s">
+        <v>399</v>
+      </c>
+      <c r="O97" t="s">
+        <v>400</v>
+      </c>
+      <c r="P97" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>35</v>
+      </c>
+      <c r="R97" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="98" spans="13:18">
+      <c r="M98" t="s">
+        <v>17</v>
+      </c>
+      <c r="N98" t="s">
+        <v>401</v>
+      </c>
+      <c r="O98" t="s">
+        <v>402</v>
+      </c>
+      <c r="P98" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>35</v>
+      </c>
+      <c r="R98" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="99" spans="13:18">
+      <c r="M99" t="s">
+        <v>17</v>
+      </c>
+      <c r="N99" t="s">
+        <v>403</v>
+      </c>
+      <c r="O99" t="s">
+        <v>404</v>
+      </c>
+      <c r="P99" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>35</v>
+      </c>
+      <c r="R99" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="100" spans="13:18">
+      <c r="M100" t="s">
+        <v>17</v>
+      </c>
+      <c r="N100" t="s">
+        <v>405</v>
+      </c>
+      <c r="O100" t="s">
+        <v>406</v>
+      </c>
+      <c r="P100" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>35</v>
+      </c>
+      <c r="R100" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="101" spans="13:18">
+      <c r="M101" t="s">
+        <v>17</v>
+      </c>
+      <c r="N101" t="s">
+        <v>407</v>
+      </c>
+      <c r="O101" t="s">
+        <v>408</v>
+      </c>
+      <c r="P101" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>35</v>
+      </c>
+      <c r="R101" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="102" spans="13:18">
+      <c r="M102" t="s">
+        <v>17</v>
+      </c>
+      <c r="N102" t="s">
+        <v>409</v>
+      </c>
+      <c r="O102" t="s">
+        <v>410</v>
+      </c>
+      <c r="P102" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>35</v>
+      </c>
+      <c r="R102" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="103" spans="13:18">
+      <c r="M103" t="s">
+        <v>17</v>
+      </c>
+      <c r="N103" t="s">
+        <v>411</v>
+      </c>
+      <c r="O103" t="s">
+        <v>412</v>
+      </c>
+      <c r="P103" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>35</v>
+      </c>
+      <c r="R103" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="104" spans="13:18">
+      <c r="M104" t="s">
+        <v>17</v>
+      </c>
+      <c r="N104" t="s">
+        <v>413</v>
+      </c>
+      <c r="O104" t="s">
+        <v>414</v>
+      </c>
+      <c r="P104" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>35</v>
+      </c>
+      <c r="R104" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="105" spans="13:18">
+      <c r="M105" t="s">
+        <v>17</v>
+      </c>
+      <c r="N105" t="s">
+        <v>415</v>
+      </c>
+      <c r="O105" t="s">
+        <v>416</v>
+      </c>
+      <c r="P105" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>35</v>
+      </c>
+      <c r="R105" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="106" spans="13:18">
+      <c r="M106" t="s">
+        <v>17</v>
+      </c>
+      <c r="N106" t="s">
+        <v>417</v>
+      </c>
+      <c r="O106" t="s">
+        <v>418</v>
+      </c>
+      <c r="P106" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>35</v>
+      </c>
+      <c r="R106" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="107" spans="13:18">
+      <c r="M107" t="s">
+        <v>17</v>
+      </c>
+      <c r="N107" t="s">
+        <v>419</v>
+      </c>
+      <c r="O107" t="s">
+        <v>420</v>
+      </c>
+      <c r="P107" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>35</v>
+      </c>
+      <c r="R107" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="108" spans="13:18">
+      <c r="M108" t="s">
+        <v>17</v>
+      </c>
+      <c r="N108" t="s">
+        <v>421</v>
+      </c>
+      <c r="O108" t="s">
+        <v>422</v>
+      </c>
+      <c r="P108" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>35</v>
+      </c>
+      <c r="R108" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="109" spans="13:18">
+      <c r="M109" t="s">
+        <v>17</v>
+      </c>
+      <c r="N109" t="s">
+        <v>423</v>
+      </c>
+      <c r="O109" t="s">
+        <v>424</v>
+      </c>
+      <c r="P109" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>35</v>
+      </c>
+      <c r="R109" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="110" spans="13:18">
+      <c r="M110" t="s">
+        <v>17</v>
+      </c>
+      <c r="N110" t="s">
+        <v>425</v>
+      </c>
+      <c r="O110" t="s">
+        <v>426</v>
+      </c>
+      <c r="P110" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>35</v>
+      </c>
+      <c r="R110" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_JPN/SysSettings.xlsx
+++ b/VerveStacks_JPN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E171CAAD-095A-451A-A57E-A437606FA987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC31F7EB-0F75-44EC-8E5A-E3C9E2F7FF97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_JPN/SysSettings.xlsx
+++ b/VerveStacks_JPN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC31F7EB-0F75-44EC-8E5A-E3C9E2F7FF97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342F616F-B444-4F97-AD50-A4DFD75C8FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_JPN/SysSettings.xlsx
+++ b/VerveStacks_JPN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342F616F-B444-4F97-AD50-A4DFD75C8FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{783944F5-B908-4A4D-BB4A-56EE641182A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_JPN/SysSettings.xlsx
+++ b/VerveStacks_JPN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{783944F5-B908-4A4D-BB4A-56EE641182A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE14C84-AEC4-4BE5-A502-F5D84D618F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_JPN/SysSettings.xlsx
+++ b/VerveStacks_JPN/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE14C84-AEC4-4BE5-A502-F5D84D618F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82596406-ACCF-407C-892F-F649F0F96A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="428">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -674,6 +674,9 @@
   </si>
   <si>
     <t>OIL</t>
+  </si>
+  <si>
+    <t>cap_bnd</t>
   </si>
   <si>
     <t>JPN</t>
@@ -3709,7 +3712,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F4" t="s">
         <v>36</v>
@@ -3792,7 +3795,7 @@
         <v>16</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>10</v>
@@ -3824,10 +3827,10 @@
         <v>17</v>
       </c>
       <c r="N5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P5" t="s">
         <v>25</v>
@@ -3836,7 +3839,7 @@
         <v>35</v>
       </c>
       <c r="R5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="2:18">
@@ -3853,10 +3856,10 @@
         <v>17</v>
       </c>
       <c r="N6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P6" t="s">
         <v>25</v>
@@ -3865,7 +3868,7 @@
         <v>35</v>
       </c>
       <c r="R6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="2:18">
@@ -3882,10 +3885,10 @@
         <v>17</v>
       </c>
       <c r="N7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P7" t="s">
         <v>25</v>
@@ -3894,7 +3897,7 @@
         <v>35</v>
       </c>
       <c r="R7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="2:18">
@@ -3911,10 +3914,10 @@
         <v>17</v>
       </c>
       <c r="N8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P8" t="s">
         <v>25</v>
@@ -3923,7 +3926,7 @@
         <v>35</v>
       </c>
       <c r="R8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="2:18">
@@ -3940,10 +3943,10 @@
         <v>17</v>
       </c>
       <c r="N9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P9" t="s">
         <v>25</v>
@@ -3952,7 +3955,7 @@
         <v>35</v>
       </c>
       <c r="R9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="2:18">
@@ -3969,10 +3972,10 @@
         <v>17</v>
       </c>
       <c r="N10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P10" t="s">
         <v>25</v>
@@ -3981,7 +3984,7 @@
         <v>35</v>
       </c>
       <c r="R10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="2:18">
@@ -3998,10 +4001,10 @@
         <v>17</v>
       </c>
       <c r="N11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P11" t="s">
         <v>25</v>
@@ -4010,7 +4013,7 @@
         <v>35</v>
       </c>
       <c r="R11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" spans="2:18">
@@ -4027,10 +4030,10 @@
         <v>17</v>
       </c>
       <c r="N12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P12" t="s">
         <v>25</v>
@@ -4039,7 +4042,7 @@
         <v>35</v>
       </c>
       <c r="R12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="2:18">
@@ -4056,10 +4059,10 @@
         <v>17</v>
       </c>
       <c r="N13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P13" t="s">
         <v>25</v>
@@ -4068,7 +4071,7 @@
         <v>35</v>
       </c>
       <c r="R13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="2:18">
@@ -4088,10 +4091,10 @@
         <v>17</v>
       </c>
       <c r="N14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P14" t="s">
         <v>25</v>
@@ -4100,7 +4103,7 @@
         <v>35</v>
       </c>
       <c r="R14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="2:18">
@@ -4120,10 +4123,10 @@
         <v>17</v>
       </c>
       <c r="N15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P15" t="s">
         <v>25</v>
@@ -4132,7 +4135,7 @@
         <v>35</v>
       </c>
       <c r="R15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="2:18">
@@ -4161,10 +4164,10 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P16" t="s">
         <v>25</v>
@@ -4173,7 +4176,7 @@
         <v>35</v>
       </c>
       <c r="R16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="2:18">
@@ -4193,10 +4196,10 @@
         <v>17</v>
       </c>
       <c r="N17" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O17" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P17" t="s">
         <v>25</v>
@@ -4205,7 +4208,7 @@
         <v>35</v>
       </c>
       <c r="R17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18" spans="2:18">
@@ -4225,10 +4228,10 @@
         <v>17</v>
       </c>
       <c r="N18" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P18" t="s">
         <v>25</v>
@@ -4237,7 +4240,7 @@
         <v>35</v>
       </c>
       <c r="R18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19" spans="2:18">
@@ -4257,10 +4260,10 @@
         <v>17</v>
       </c>
       <c r="N19" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P19" t="s">
         <v>25</v>
@@ -4269,7 +4272,7 @@
         <v>35</v>
       </c>
       <c r="R19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20" spans="2:18">
@@ -4289,10 +4292,10 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O20" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P20" t="s">
         <v>25</v>
@@ -4301,7 +4304,7 @@
         <v>35</v>
       </c>
       <c r="R20" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="2:18">
@@ -4327,10 +4330,10 @@
         <v>17</v>
       </c>
       <c r="N21" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O21" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P21" t="s">
         <v>25</v>
@@ -4339,7 +4342,7 @@
         <v>35</v>
       </c>
       <c r="R21" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" spans="2:18">
@@ -4359,10 +4362,10 @@
         <v>17</v>
       </c>
       <c r="N22" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O22" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P22" t="s">
         <v>25</v>
@@ -4371,7 +4374,7 @@
         <v>35</v>
       </c>
       <c r="R22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23" spans="2:18">
@@ -4388,10 +4391,10 @@
         <v>17</v>
       </c>
       <c r="N23" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O23" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P23" t="s">
         <v>25</v>
@@ -4400,7 +4403,7 @@
         <v>35</v>
       </c>
       <c r="R23" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" spans="2:18">
@@ -4417,10 +4420,10 @@
         <v>17</v>
       </c>
       <c r="N24" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O24" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P24" t="s">
         <v>25</v>
@@ -4429,7 +4432,7 @@
         <v>35</v>
       </c>
       <c r="R24" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="2:18">
@@ -4437,10 +4440,10 @@
         <v>17</v>
       </c>
       <c r="N25" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O25" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P25" t="s">
         <v>25</v>
@@ -4449,7 +4452,7 @@
         <v>35</v>
       </c>
       <c r="R25" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" spans="2:18">
@@ -4457,10 +4460,10 @@
         <v>17</v>
       </c>
       <c r="N26" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O26" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P26" t="s">
         <v>25</v>
@@ -4469,7 +4472,7 @@
         <v>35</v>
       </c>
       <c r="R26" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="2:18">
@@ -4477,10 +4480,10 @@
         <v>17</v>
       </c>
       <c r="N27" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O27" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P27" t="s">
         <v>25</v>
@@ -4489,7 +4492,7 @@
         <v>35</v>
       </c>
       <c r="R27" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="2:18">
@@ -4497,10 +4500,10 @@
         <v>17</v>
       </c>
       <c r="N28" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O28" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P28" t="s">
         <v>25</v>
@@ -4509,7 +4512,7 @@
         <v>35</v>
       </c>
       <c r="R28" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="29" spans="2:18">
@@ -4517,10 +4520,10 @@
         <v>17</v>
       </c>
       <c r="N29" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O29" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P29" t="s">
         <v>25</v>
@@ -4529,7 +4532,7 @@
         <v>35</v>
       </c>
       <c r="R29" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30" spans="2:18">
@@ -4537,10 +4540,10 @@
         <v>17</v>
       </c>
       <c r="N30" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P30" t="s">
         <v>25</v>
@@ -4549,7 +4552,7 @@
         <v>35</v>
       </c>
       <c r="R30" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31" spans="2:18">
@@ -4557,10 +4560,10 @@
         <v>17</v>
       </c>
       <c r="N31" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O31" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P31" t="s">
         <v>25</v>
@@ -4569,7 +4572,7 @@
         <v>35</v>
       </c>
       <c r="R31" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="32" spans="2:18">
@@ -4577,10 +4580,10 @@
         <v>17</v>
       </c>
       <c r="N32" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O32" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P32" t="s">
         <v>25</v>
@@ -4589,7 +4592,7 @@
         <v>35</v>
       </c>
       <c r="R32" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33" spans="13:18">
@@ -4597,10 +4600,10 @@
         <v>17</v>
       </c>
       <c r="N33" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O33" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P33" t="s">
         <v>25</v>
@@ -4609,7 +4612,7 @@
         <v>35</v>
       </c>
       <c r="R33" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="34" spans="13:18">
@@ -4617,10 +4620,10 @@
         <v>17</v>
       </c>
       <c r="N34" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O34" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P34" t="s">
         <v>25</v>
@@ -4629,7 +4632,7 @@
         <v>35</v>
       </c>
       <c r="R34" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="35" spans="13:18">
@@ -4637,10 +4640,10 @@
         <v>17</v>
       </c>
       <c r="N35" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O35" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P35" t="s">
         <v>25</v>
@@ -4649,7 +4652,7 @@
         <v>35</v>
       </c>
       <c r="R35" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="36" spans="13:18">
@@ -4657,10 +4660,10 @@
         <v>17</v>
       </c>
       <c r="N36" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O36" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P36" t="s">
         <v>25</v>
@@ -4669,7 +4672,7 @@
         <v>35</v>
       </c>
       <c r="R36" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="37" spans="13:18">
@@ -4677,10 +4680,10 @@
         <v>17</v>
       </c>
       <c r="N37" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O37" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P37" t="s">
         <v>25</v>
@@ -4689,7 +4692,7 @@
         <v>35</v>
       </c>
       <c r="R37" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="38" spans="13:18">
@@ -4697,10 +4700,10 @@
         <v>17</v>
       </c>
       <c r="N38" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O38" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P38" t="s">
         <v>25</v>
@@ -4709,7 +4712,7 @@
         <v>35</v>
       </c>
       <c r="R38" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="39" spans="13:18">
@@ -4717,10 +4720,10 @@
         <v>17</v>
       </c>
       <c r="N39" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O39" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P39" t="s">
         <v>25</v>
@@ -4729,7 +4732,7 @@
         <v>35</v>
       </c>
       <c r="R39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="40" spans="13:18">
@@ -4737,10 +4740,10 @@
         <v>17</v>
       </c>
       <c r="N40" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O40" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P40" t="s">
         <v>25</v>
@@ -4749,7 +4752,7 @@
         <v>35</v>
       </c>
       <c r="R40" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="41" spans="13:18">
@@ -4757,10 +4760,10 @@
         <v>17</v>
       </c>
       <c r="N41" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O41" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P41" t="s">
         <v>25</v>
@@ -4769,7 +4772,7 @@
         <v>35</v>
       </c>
       <c r="R41" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="42" spans="13:18">
@@ -4777,10 +4780,10 @@
         <v>17</v>
       </c>
       <c r="N42" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O42" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P42" t="s">
         <v>25</v>
@@ -4789,7 +4792,7 @@
         <v>35</v>
       </c>
       <c r="R42" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="43" spans="13:18">
@@ -4797,10 +4800,10 @@
         <v>17</v>
       </c>
       <c r="N43" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O43" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P43" t="s">
         <v>25</v>
@@ -4809,7 +4812,7 @@
         <v>35</v>
       </c>
       <c r="R43" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="44" spans="13:18">
@@ -4817,10 +4820,10 @@
         <v>17</v>
       </c>
       <c r="N44" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O44" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P44" t="s">
         <v>25</v>
@@ -4829,7 +4832,7 @@
         <v>35</v>
       </c>
       <c r="R44" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="45" spans="13:18">
@@ -4837,10 +4840,10 @@
         <v>17</v>
       </c>
       <c r="N45" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O45" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P45" t="s">
         <v>25</v>
@@ -4849,7 +4852,7 @@
         <v>35</v>
       </c>
       <c r="R45" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="46" spans="13:18">
@@ -4857,10 +4860,10 @@
         <v>17</v>
       </c>
       <c r="N46" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O46" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P46" t="s">
         <v>25</v>
@@ -4869,7 +4872,7 @@
         <v>35</v>
       </c>
       <c r="R46" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="47" spans="13:18">
@@ -4877,10 +4880,10 @@
         <v>17</v>
       </c>
       <c r="N47" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O47" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P47" t="s">
         <v>25</v>
@@ -4889,7 +4892,7 @@
         <v>35</v>
       </c>
       <c r="R47" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="48" spans="13:18">
@@ -4897,10 +4900,10 @@
         <v>17</v>
       </c>
       <c r="N48" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O48" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P48" t="s">
         <v>25</v>
@@ -4909,7 +4912,7 @@
         <v>35</v>
       </c>
       <c r="R48" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="49" spans="13:18">
@@ -4917,10 +4920,10 @@
         <v>17</v>
       </c>
       <c r="N49" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O49" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P49" t="s">
         <v>25</v>
@@ -4929,7 +4932,7 @@
         <v>35</v>
       </c>
       <c r="R49" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="50" spans="13:18">
@@ -4937,10 +4940,10 @@
         <v>17</v>
       </c>
       <c r="N50" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O50" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P50" t="s">
         <v>25</v>
@@ -4949,7 +4952,7 @@
         <v>35</v>
       </c>
       <c r="R50" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="51" spans="13:18">
@@ -4957,10 +4960,10 @@
         <v>17</v>
       </c>
       <c r="N51" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O51" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P51" t="s">
         <v>25</v>
@@ -4969,7 +4972,7 @@
         <v>35</v>
       </c>
       <c r="R51" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="52" spans="13:18">
@@ -4977,10 +4980,10 @@
         <v>17</v>
       </c>
       <c r="N52" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O52" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P52" t="s">
         <v>25</v>
@@ -4989,7 +4992,7 @@
         <v>35</v>
       </c>
       <c r="R52" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="53" spans="13:18">
@@ -4997,10 +5000,10 @@
         <v>17</v>
       </c>
       <c r="N53" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O53" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P53" t="s">
         <v>25</v>
@@ -5009,7 +5012,7 @@
         <v>35</v>
       </c>
       <c r="R53" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="54" spans="13:18">
@@ -5017,10 +5020,10 @@
         <v>17</v>
       </c>
       <c r="N54" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O54" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P54" t="s">
         <v>25</v>
@@ -5029,7 +5032,7 @@
         <v>35</v>
       </c>
       <c r="R54" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="55" spans="13:18">
@@ -5037,10 +5040,10 @@
         <v>17</v>
       </c>
       <c r="N55" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O55" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P55" t="s">
         <v>25</v>
@@ -5049,7 +5052,7 @@
         <v>35</v>
       </c>
       <c r="R55" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="13:18">
@@ -5057,10 +5060,10 @@
         <v>17</v>
       </c>
       <c r="N56" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P56" t="s">
         <v>25</v>
@@ -5069,7 +5072,7 @@
         <v>35</v>
       </c>
       <c r="R56" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="57" spans="13:18">
@@ -5077,10 +5080,10 @@
         <v>17</v>
       </c>
       <c r="N57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O57" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P57" t="s">
         <v>25</v>
@@ -5089,7 +5092,7 @@
         <v>35</v>
       </c>
       <c r="R57" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="58" spans="13:18">
@@ -5097,10 +5100,10 @@
         <v>17</v>
       </c>
       <c r="N58" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O58" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P58" t="s">
         <v>25</v>
@@ -5109,7 +5112,7 @@
         <v>35</v>
       </c>
       <c r="R58" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="59" spans="13:18">
@@ -5117,10 +5120,10 @@
         <v>17</v>
       </c>
       <c r="N59" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O59" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P59" t="s">
         <v>25</v>
@@ -5129,7 +5132,7 @@
         <v>35</v>
       </c>
       <c r="R59" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="60" spans="13:18">
@@ -5137,10 +5140,10 @@
         <v>17</v>
       </c>
       <c r="N60" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O60" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P60" t="s">
         <v>25</v>
@@ -5149,7 +5152,7 @@
         <v>35</v>
       </c>
       <c r="R60" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="61" spans="13:18">
@@ -5157,10 +5160,10 @@
         <v>17</v>
       </c>
       <c r="N61" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O61" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P61" t="s">
         <v>25</v>
@@ -5169,7 +5172,7 @@
         <v>35</v>
       </c>
       <c r="R61" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="62" spans="13:18">
@@ -5177,10 +5180,10 @@
         <v>17</v>
       </c>
       <c r="N62" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O62" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P62" t="s">
         <v>25</v>
@@ -5189,7 +5192,7 @@
         <v>35</v>
       </c>
       <c r="R62" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="63" spans="13:18">
@@ -5197,10 +5200,10 @@
         <v>17</v>
       </c>
       <c r="N63" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O63" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P63" t="s">
         <v>25</v>
@@ -5209,7 +5212,7 @@
         <v>35</v>
       </c>
       <c r="R63" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="64" spans="13:18">
@@ -5217,10 +5220,10 @@
         <v>17</v>
       </c>
       <c r="N64" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O64" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P64" t="s">
         <v>25</v>
@@ -5229,7 +5232,7 @@
         <v>35</v>
       </c>
       <c r="R64" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="65" spans="13:18">
@@ -5237,10 +5240,10 @@
         <v>17</v>
       </c>
       <c r="N65" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O65" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P65" t="s">
         <v>25</v>
@@ -5249,7 +5252,7 @@
         <v>35</v>
       </c>
       <c r="R65" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="66" spans="13:18">
@@ -5257,10 +5260,10 @@
         <v>17</v>
       </c>
       <c r="N66" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O66" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P66" t="s">
         <v>25</v>
@@ -5269,7 +5272,7 @@
         <v>35</v>
       </c>
       <c r="R66" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="67" spans="13:18">
@@ -5277,10 +5280,10 @@
         <v>17</v>
       </c>
       <c r="N67" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O67" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P67" t="s">
         <v>25</v>
@@ -5289,7 +5292,7 @@
         <v>35</v>
       </c>
       <c r="R67" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="68" spans="13:18">
@@ -5297,10 +5300,10 @@
         <v>17</v>
       </c>
       <c r="N68" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O68" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P68" t="s">
         <v>25</v>
@@ -5309,7 +5312,7 @@
         <v>35</v>
       </c>
       <c r="R68" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="69" spans="13:18">
@@ -5317,10 +5320,10 @@
         <v>17</v>
       </c>
       <c r="N69" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O69" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P69" t="s">
         <v>25</v>
@@ -5329,7 +5332,7 @@
         <v>35</v>
       </c>
       <c r="R69" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="70" spans="13:18">
@@ -5337,10 +5340,10 @@
         <v>17</v>
       </c>
       <c r="N70" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O70" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P70" t="s">
         <v>25</v>
@@ -5349,7 +5352,7 @@
         <v>35</v>
       </c>
       <c r="R70" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="71" spans="13:18">
@@ -5357,10 +5360,10 @@
         <v>17</v>
       </c>
       <c r="N71" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O71" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P71" t="s">
         <v>25</v>
@@ -5369,7 +5372,7 @@
         <v>35</v>
       </c>
       <c r="R71" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="72" spans="13:18">
@@ -5377,10 +5380,10 @@
         <v>17</v>
       </c>
       <c r="N72" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O72" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P72" t="s">
         <v>25</v>
@@ -5389,7 +5392,7 @@
         <v>35</v>
       </c>
       <c r="R72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="13:18">
@@ -5397,10 +5400,10 @@
         <v>17</v>
       </c>
       <c r="N73" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O73" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P73" t="s">
         <v>25</v>
@@ -5409,7 +5412,7 @@
         <v>35</v>
       </c>
       <c r="R73" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="74" spans="13:18">
@@ -5417,10 +5420,10 @@
         <v>17</v>
       </c>
       <c r="N74" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O74" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P74" t="s">
         <v>25</v>
@@ -5429,7 +5432,7 @@
         <v>35</v>
       </c>
       <c r="R74" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="75" spans="13:18">
@@ -5437,10 +5440,10 @@
         <v>17</v>
       </c>
       <c r="N75" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O75" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P75" t="s">
         <v>25</v>
@@ -5449,7 +5452,7 @@
         <v>35</v>
       </c>
       <c r="R75" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="76" spans="13:18">
@@ -5457,10 +5460,10 @@
         <v>17</v>
       </c>
       <c r="N76" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O76" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P76" t="s">
         <v>25</v>
@@ -5469,7 +5472,7 @@
         <v>35</v>
       </c>
       <c r="R76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="77" spans="13:18">
@@ -5477,10 +5480,10 @@
         <v>17</v>
       </c>
       <c r="N77" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O77" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P77" t="s">
         <v>25</v>
@@ -5489,7 +5492,7 @@
         <v>35</v>
       </c>
       <c r="R77" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="78" spans="13:18">
@@ -5497,10 +5500,10 @@
         <v>17</v>
       </c>
       <c r="N78" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O78" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P78" t="s">
         <v>25</v>
@@ -5509,7 +5512,7 @@
         <v>35</v>
       </c>
       <c r="R78" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="79" spans="13:18">
@@ -5517,10 +5520,10 @@
         <v>17</v>
       </c>
       <c r="N79" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O79" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P79" t="s">
         <v>25</v>
@@ -5529,7 +5532,7 @@
         <v>35</v>
       </c>
       <c r="R79" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="80" spans="13:18">
@@ -5537,10 +5540,10 @@
         <v>17</v>
       </c>
       <c r="N80" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O80" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P80" t="s">
         <v>25</v>
@@ -5549,7 +5552,7 @@
         <v>35</v>
       </c>
       <c r="R80" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="81" spans="13:18">
@@ -5557,10 +5560,10 @@
         <v>17</v>
       </c>
       <c r="N81" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O81" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P81" t="s">
         <v>25</v>
@@ -5569,7 +5572,7 @@
         <v>35</v>
       </c>
       <c r="R81" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="82" spans="13:18">
@@ -5577,10 +5580,10 @@
         <v>17</v>
       </c>
       <c r="N82" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O82" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P82" t="s">
         <v>25</v>
@@ -5589,7 +5592,7 @@
         <v>35</v>
       </c>
       <c r="R82" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="83" spans="13:18">
@@ -5597,10 +5600,10 @@
         <v>17</v>
       </c>
       <c r="N83" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O83" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P83" t="s">
         <v>25</v>
@@ -5609,7 +5612,7 @@
         <v>35</v>
       </c>
       <c r="R83" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="84" spans="13:18">
@@ -5617,10 +5620,10 @@
         <v>17</v>
       </c>
       <c r="N84" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O84" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P84" t="s">
         <v>25</v>
@@ -5629,7 +5632,7 @@
         <v>35</v>
       </c>
       <c r="R84" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="85" spans="13:18">
@@ -5637,10 +5640,10 @@
         <v>17</v>
       </c>
       <c r="N85" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O85" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P85" t="s">
         <v>25</v>
@@ -5649,7 +5652,7 @@
         <v>35</v>
       </c>
       <c r="R85" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="86" spans="13:18">
@@ -5657,10 +5660,10 @@
         <v>17</v>
       </c>
       <c r="N86" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O86" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P86" t="s">
         <v>25</v>
@@ -5669,7 +5672,7 @@
         <v>35</v>
       </c>
       <c r="R86" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="87" spans="13:18">
@@ -5677,10 +5680,10 @@
         <v>17</v>
       </c>
       <c r="N87" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O87" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P87" t="s">
         <v>25</v>
@@ -5689,7 +5692,7 @@
         <v>35</v>
       </c>
       <c r="R87" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="88" spans="13:18">
@@ -5697,10 +5700,10 @@
         <v>17</v>
       </c>
       <c r="N88" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O88" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P88" t="s">
         <v>25</v>
@@ -5709,7 +5712,7 @@
         <v>35</v>
       </c>
       <c r="R88" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="89" spans="13:18">
@@ -5717,10 +5720,10 @@
         <v>17</v>
       </c>
       <c r="N89" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O89" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P89" t="s">
         <v>25</v>
@@ -5729,7 +5732,7 @@
         <v>35</v>
       </c>
       <c r="R89" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="90" spans="13:18">
@@ -5737,10 +5740,10 @@
         <v>17</v>
       </c>
       <c r="N90" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O90" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P90" t="s">
         <v>25</v>
@@ -5749,7 +5752,7 @@
         <v>35</v>
       </c>
       <c r="R90" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="91" spans="13:18">
@@ -5757,10 +5760,10 @@
         <v>17</v>
       </c>
       <c r="N91" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O91" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P91" t="s">
         <v>25</v>
@@ -5769,7 +5772,7 @@
         <v>35</v>
       </c>
       <c r="R91" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="92" spans="13:18">
@@ -5777,10 +5780,10 @@
         <v>17</v>
       </c>
       <c r="N92" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O92" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P92" t="s">
         <v>25</v>
@@ -5789,7 +5792,7 @@
         <v>35</v>
       </c>
       <c r="R92" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="93" spans="13:18">
@@ -5797,10 +5800,10 @@
         <v>17</v>
       </c>
       <c r="N93" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O93" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P93" t="s">
         <v>25</v>
@@ -5809,7 +5812,7 @@
         <v>35</v>
       </c>
       <c r="R93" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="94" spans="13:18">
@@ -5817,10 +5820,10 @@
         <v>17</v>
       </c>
       <c r="N94" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O94" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P94" t="s">
         <v>25</v>
@@ -5829,7 +5832,7 @@
         <v>35</v>
       </c>
       <c r="R94" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="95" spans="13:18">
@@ -5837,10 +5840,10 @@
         <v>17</v>
       </c>
       <c r="N95" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O95" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P95" t="s">
         <v>25</v>
@@ -5849,7 +5852,7 @@
         <v>35</v>
       </c>
       <c r="R95" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="96" spans="13:18">
@@ -5857,10 +5860,10 @@
         <v>17</v>
       </c>
       <c r="N96" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O96" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P96" t="s">
         <v>25</v>
@@ -5869,7 +5872,7 @@
         <v>35</v>
       </c>
       <c r="R96" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="97" spans="13:18">
@@ -5877,10 +5880,10 @@
         <v>17</v>
       </c>
       <c r="N97" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O97" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P97" t="s">
         <v>25</v>
@@ -5889,7 +5892,7 @@
         <v>35</v>
       </c>
       <c r="R97" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="98" spans="13:18">
@@ -5897,10 +5900,10 @@
         <v>17</v>
       </c>
       <c r="N98" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O98" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P98" t="s">
         <v>25</v>
@@ -5909,7 +5912,7 @@
         <v>35</v>
       </c>
       <c r="R98" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="99" spans="13:18">
@@ -5917,10 +5920,10 @@
         <v>17</v>
       </c>
       <c r="N99" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O99" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P99" t="s">
         <v>25</v>
@@ -5929,7 +5932,7 @@
         <v>35</v>
       </c>
       <c r="R99" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="100" spans="13:18">
@@ -5937,10 +5940,10 @@
         <v>17</v>
       </c>
       <c r="N100" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O100" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P100" t="s">
         <v>25</v>
@@ -5949,7 +5952,7 @@
         <v>35</v>
       </c>
       <c r="R100" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="101" spans="13:18">
@@ -5957,10 +5960,10 @@
         <v>17</v>
       </c>
       <c r="N101" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O101" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P101" t="s">
         <v>25</v>
@@ -5969,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="R101" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="102" spans="13:18">
@@ -5977,10 +5980,10 @@
         <v>17</v>
       </c>
       <c r="N102" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O102" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P102" t="s">
         <v>25</v>
@@ -5989,7 +5992,7 @@
         <v>35</v>
       </c>
       <c r="R102" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="103" spans="13:18">
@@ -5997,10 +6000,10 @@
         <v>17</v>
       </c>
       <c r="N103" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O103" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P103" t="s">
         <v>25</v>
@@ -6009,7 +6012,7 @@
         <v>35</v>
       </c>
       <c r="R103" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="104" spans="13:18">
@@ -6017,10 +6020,10 @@
         <v>17</v>
       </c>
       <c r="N104" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O104" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P104" t="s">
         <v>25</v>
@@ -6029,7 +6032,7 @@
         <v>35</v>
       </c>
       <c r="R104" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="105" spans="13:18">
@@ -6037,10 +6040,10 @@
         <v>17</v>
       </c>
       <c r="N105" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O105" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P105" t="s">
         <v>25</v>
@@ -6049,7 +6052,7 @@
         <v>35</v>
       </c>
       <c r="R105" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="106" spans="13:18">
@@ -6057,10 +6060,10 @@
         <v>17</v>
       </c>
       <c r="N106" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O106" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P106" t="s">
         <v>25</v>
@@ -6069,7 +6072,7 @@
         <v>35</v>
       </c>
       <c r="R106" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="107" spans="13:18">
@@ -6077,10 +6080,10 @@
         <v>17</v>
       </c>
       <c r="N107" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O107" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P107" t="s">
         <v>25</v>
@@ -6089,7 +6092,7 @@
         <v>35</v>
       </c>
       <c r="R107" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="108" spans="13:18">
@@ -6097,10 +6100,10 @@
         <v>17</v>
       </c>
       <c r="N108" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O108" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P108" t="s">
         <v>25</v>
@@ -6109,7 +6112,7 @@
         <v>35</v>
       </c>
       <c r="R108" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="109" spans="13:18">
@@ -6117,10 +6120,10 @@
         <v>17</v>
       </c>
       <c r="N109" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O109" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P109" t="s">
         <v>25</v>
@@ -6129,7 +6132,7 @@
         <v>35</v>
       </c>
       <c r="R109" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="110" spans="13:18">
@@ -6137,10 +6140,10 @@
         <v>17</v>
       </c>
       <c r="N110" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O110" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P110" t="s">
         <v>25</v>
@@ -6149,7 +6152,7 @@
         <v>35</v>
       </c>
       <c r="R110" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -6440,7 +6443,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
-  <dimension ref="B1:N41"/>
+  <dimension ref="B1:N42"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="11.3984375" style="11"/>
@@ -6582,49 +6585,49 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="2:12">
-      <c r="B13" s="14" t="s">
+    <row r="11" spans="2:12">
+      <c r="D11" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12">
+      <c r="B14" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-    </row>
-    <row r="14" spans="2:12">
-      <c r="B14" s="15" t="s">
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="B15" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C15" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D15" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E15" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F15" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G15" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H15" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I15" s="15" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12">
-      <c r="D15" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" s="11">
-        <v>2222</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="16" spans="2:12">
@@ -6632,22 +6635,22 @@
         <v>66</v>
       </c>
       <c r="F16" s="11">
+        <v>2222</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="D17" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="11">
         <v>8888</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G17" s="11" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="17" spans="2:14" ht="12.75">
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
     </row>
     <row r="18" spans="2:14" ht="12.75">
       <c r="B18" s="13"/>
@@ -6671,20 +6674,16 @@
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
     </row>
-    <row r="20" spans="2:14" ht="14.25">
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="D20"/>
-      <c r="E20"/>
-      <c r="F20"/>
-      <c r="G20"/>
-      <c r="H20"/>
-      <c r="I20"/>
-      <c r="J20"/>
-      <c r="K20"/>
-      <c r="L20"/>
-      <c r="M20"/>
-      <c r="N20"/>
+    <row r="20" spans="2:14" ht="12.75">
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" spans="2:14" ht="14.25">
       <c r="B21"/>
@@ -7000,6 +6999,21 @@
       <c r="L41"/>
       <c r="M41"/>
       <c r="N41"/>
+    </row>
+    <row r="42" spans="2:14" ht="14.25">
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42"/>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/VerveStacks_JPN/SysSettings.xlsx
+++ b/VerveStacks_JPN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82596406-ACCF-407C-892F-F649F0F96A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DCD98C-EF56-42AE-825A-92CCE9035DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_JPN/SysSettings.xlsx
+++ b/VerveStacks_JPN/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DCD98C-EF56-42AE-825A-92CCE9035DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2DC3E46-0EE1-467A-BB08-B5F3DE850815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
